--- a/Weight_Data_1.xlsx
+++ b/Weight_Data_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riley\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC757F0-1AE1-4526-8B39-1ADF34ABF706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BC13992-7E1A-4D04-9AAC-60F4FE97BA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{73CCE4AA-3F2E-435E-A5F9-0E12C08AF790}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{FD833EB7-FC0C-4DB0-A199-49E8916F6AD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
-    <t>Wet Weight (g)</t>
+    <t>Net Wet Weight (g)</t>
   </si>
   <si>
-    <t>Dry Weight (g)</t>
+    <t>uncertainty</t>
   </si>
   <si>
-    <t>Uncertainty</t>
+    <t>Net Dry Weight (g)</t>
   </si>
 </sst>
 </file>
@@ -415,22 +415,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA440A8E-82D5-43DD-A17D-AEE37592C6BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A75385-1471-4E43-8D49-BB5CB2666AF9}">
   <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -476,9 +480,6 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B5">
-        <v>0.01</v>
-      </c>
       <c r="C5">
         <v>18.243999999999993</v>
       </c>
@@ -599,9 +600,6 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14">
-        <v>0.01</v>
-      </c>
       <c r="C14">
         <v>17.323999999999991</v>
       </c>
@@ -610,9 +608,6 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15">
-        <v>0.01</v>
-      </c>
       <c r="C15">
         <v>26.483999999999995</v>
       </c>
@@ -744,9 +739,6 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B25">
-        <v>0.01</v>
-      </c>
       <c r="C25">
         <v>33.233999999999995</v>
       </c>
@@ -769,9 +761,6 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <v>0.01</v>
-      </c>
       <c r="C27">
         <v>34.423999999999992</v>
       </c>
@@ -794,9 +783,6 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B29">
-        <v>0.01</v>
-      </c>
       <c r="C29">
         <v>39.014000000000003</v>
       </c>
@@ -805,9 +791,6 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B30">
-        <v>0.01</v>
-      </c>
       <c r="C30">
         <v>37.823999999999991</v>
       </c>
